--- a/data/corpus/售后FAQ.xlsx
+++ b/data/corpus/售后FAQ.xlsx
@@ -26,12 +26,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
